--- a/tools/importer/reports/import-sustainability-topic.report.xlsx
+++ b/tools/importer/reports/import-sustainability-topic.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="97">
   <si>
     <t>_reportFile</t>
   </si>
@@ -124,7 +124,7 @@
     <t>who-we-are</t>
   </si>
   <si>
-    <t>2026-05-14T16:04:39.512Z</t>
+    <t>2026-05-15T20:01:30.755Z</t>
   </si>
   <si>
     <t>Who We Are — Chevron</t>
@@ -145,7 +145,7 @@
     <t>sustainability-topic</t>
   </si>
   <si>
-    <t>2026-05-15T12:47:15.848Z</t>
+    <t>2026-05-15T20:02:02.695Z</t>
   </si>
   <si>
     <t>Climate – Chevron.com — Chevron</t>
@@ -163,7 +163,7 @@
     <t>sustainability/environment</t>
   </si>
   <si>
-    <t>2026-05-15T12:47:22.628Z</t>
+    <t>2026-05-15T20:02:10.641Z</t>
   </si>
   <si>
     <t>Environment | Chevron — Chevron</t>
@@ -181,13 +181,127 @@
     <t>sustainability/social-investment</t>
   </si>
   <si>
-    <t>2026-05-15T12:48:15.982Z</t>
+    <t>2026-05-15T20:03:03.734Z</t>
   </si>
   <si>
     <t>Social Investment | Chevron — Chevron</t>
   </si>
   <si>
     <t>https://www.chevron.com/sustainability/social-investment</t>
+  </si>
+  <si>
+    <t>what-we-do/energy.report.json</t>
+  </si>
+  <si>
+    <t>["hero-video","columns-feature","columns-feature","columns-feature","columns-feature","carousel-article"]</t>
+  </si>
+  <si>
+    <t>what-we-do/energy</t>
+  </si>
+  <si>
+    <t>what-we-do-topic</t>
+  </si>
+  <si>
+    <t>2026-05-15T20:01:40.940Z</t>
+  </si>
+  <si>
+    <t>Energy Solutions — Chevron</t>
+  </si>
+  <si>
+    <t>https://www.chevron.com/what-we-do/energy</t>
+  </si>
+  <si>
+    <t>what-we-do/technology-and-innovation.report.json</t>
+  </si>
+  <si>
+    <t>["hero-video","carousel-article","carousel-article","carousel-feature"]</t>
+  </si>
+  <si>
+    <t>what-we-do/technology-and-innovation</t>
+  </si>
+  <si>
+    <t>2026-05-15T20:01:52.392Z</t>
+  </si>
+  <si>
+    <t>Technology and Innovation — Chevron</t>
+  </si>
+  <si>
+    <t>https://www.chevron.com/what-we-do/technology-and-innovation</t>
+  </si>
+  <si>
+    <t>who-we-are/culture.report.json</t>
+  </si>
+  <si>
+    <t>["hero-video","columns-feature","columns-feature","columns-feature","columns-feature","carousel-article","carousel-image","carousel-feature","cards-data"]</t>
+  </si>
+  <si>
+    <t>who-we-are/culture</t>
+  </si>
+  <si>
+    <t>who-we-are-topic</t>
+  </si>
+  <si>
+    <t>2026-05-15T15:34:27.138Z</t>
+  </si>
+  <si>
+    <t>Chevron Culture — Chevron</t>
+  </si>
+  <si>
+    <t>https://www.chevron.com/who-we-are/culture</t>
+  </si>
+  <si>
+    <t>who-we-are/history.report.json</t>
+  </si>
+  <si>
+    <t>["columns-brand","columns-brand","columns-brand","columns-brand","carousel-article","carousel-image","carousel-image","carousel-image","carousel-image","carousel-image","carousel-image","carousel-image","carousel-image","carousel-image","carousel-image","carousel-image","tabs-timeline"]</t>
+  </si>
+  <si>
+    <t>who-we-are/history</t>
+  </si>
+  <si>
+    <t>2026-05-15T15:35:01.308Z</t>
+  </si>
+  <si>
+    <t>Our History | Chevron — Chevron</t>
+  </si>
+  <si>
+    <t>https://www.chevron.com/who-we-are/history</t>
+  </si>
+  <si>
+    <t>who-we-are/leadership.report.json</t>
+  </si>
+  <si>
+    <t>["hero-video","cards-data","cards-data"]</t>
+  </si>
+  <si>
+    <t>who-we-are/leadership</t>
+  </si>
+  <si>
+    <t>2026-05-15T15:34:40.279Z</t>
+  </si>
+  <si>
+    <t>Chevron Leadership — Chevron</t>
+  </si>
+  <si>
+    <t>https://www.chevron.com/who-we-are/leadership</t>
+  </si>
+  <si>
+    <t>who-we-are/our-brands.report.json</t>
+  </si>
+  <si>
+    <t>["hero-video","columns-brand","columns-brand","columns-brand","columns-brand","columns-brand","columns-mosaic"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-brands</t>
+  </si>
+  <si>
+    <t>2026-05-15T15:34:33.105Z</t>
+  </si>
+  <si>
+    <t>Our Brands — Chevron</t>
+  </si>
+  <si>
+    <t>https://www.chevron.com/who-we-are/our-brands</t>
   </si>
 </sst>
 </file>
@@ -576,12 +690,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="1" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="8" width="50" customWidth="1"/>
@@ -821,6 +934,162 @@
         <v>58</v>
       </c>
     </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" t="s">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tools/importer/reports/import-sustainability-topic.report.xlsx
+++ b/tools/importer/reports/import-sustainability-topic.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["carousel-hero","hero-marquee","columns-mosaic","carousel-article"]</t>
+    <t>["carousel-hero","hero-marquee","columns-mosaic","columns-feature","carousel-article"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-05-14T20:28:19.380Z</t>
+    <t>2026-05-15T20:42:01.285Z</t>
   </si>
   <si>
     <t>Chevron Corporation - Human Energy — Chevron</t>
@@ -70,7 +70,7 @@
     <t>investors</t>
   </si>
   <si>
-    <t>2026-05-14T22:08:04.337Z</t>
+    <t>2026-05-15T20:04:11.171Z</t>
   </si>
   <si>
     <t>Chevron Investors: Delivering Strong Results — Chevron</t>
@@ -82,13 +82,16 @@
     <t>sustainability.report.json</t>
   </si>
   <si>
-    <t>["hero-video","embed-map","cards-topic","carousel-article"]</t>
+    <t>["hero-video","carousel-article","cards-topic","columns-data"]</t>
   </si>
   <si>
     <t>sustainability</t>
   </si>
   <si>
-    <t>2026-05-14T20:00:15.122Z</t>
+    <t>sustainability-topic</t>
+  </si>
+  <si>
+    <t>2026-05-15T20:42:34.199Z</t>
   </si>
   <si>
     <t>Sustainability — Chevron.com — Chevron</t>
@@ -100,13 +103,13 @@
     <t>what-we-do.report.json</t>
   </si>
   <si>
-    <t>["hero-video","columns-mosaic","columns-mosaic","carousel-article"]</t>
+    <t>["carousel-article"]</t>
   </si>
   <si>
     <t>what-we-do</t>
   </si>
   <si>
-    <t>2026-05-14T20:00:05.630Z</t>
+    <t>2026-05-15T20:42:22.333Z</t>
   </si>
   <si>
     <t>What We Do — Chevron</t>
@@ -142,9 +145,6 @@
     <t>sustainability/climate</t>
   </si>
   <si>
-    <t>sustainability-topic</t>
-  </si>
-  <si>
     <t>2026-05-15T20:02:02.695Z</t>
   </si>
   <si>
@@ -241,7 +241,7 @@
     <t>who-we-are-topic</t>
   </si>
   <si>
-    <t>2026-05-15T15:34:27.138Z</t>
+    <t>2026-05-15T20:03:13.653Z</t>
   </si>
   <si>
     <t>Chevron Culture — Chevron</t>
@@ -259,7 +259,7 @@
     <t>who-we-are/history</t>
   </si>
   <si>
-    <t>2026-05-15T15:35:01.308Z</t>
+    <t>2026-05-15T20:03:50.372Z</t>
   </si>
   <si>
     <t>Our History | Chevron — Chevron</t>
@@ -277,7 +277,7 @@
     <t>who-we-are/leadership</t>
   </si>
   <si>
-    <t>2026-05-15T15:34:40.279Z</t>
+    <t>2026-05-15T20:03:29.275Z</t>
   </si>
   <si>
     <t>Chevron Leadership — Chevron</t>
@@ -295,7 +295,7 @@
     <t>who-we-are/our-brands</t>
   </si>
   <si>
-    <t>2026-05-15T15:34:33.105Z</t>
+    <t>2026-05-15T20:03:23.337Z</t>
   </si>
   <si>
     <t>Our Brands — Chevron</t>
@@ -792,85 +792,85 @@
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
         <v>44</v>
@@ -896,7 +896,7 @@
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
         <v>50</v>
@@ -922,7 +922,7 @@
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
         <v>56</v>
